--- a/codebook.xlsx
+++ b/codebook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dile/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dile/Desktop/phd/sol/Third Year/chiir2027/results/repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A747774-8B0D-674E-9D18-57843B8187F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2CC701A-3977-1948-8978-85C30A8EF0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15520" yWindow="760" windowWidth="14300" windowHeight="17580" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reasoning codebook" sheetId="1" r:id="rId1"/>
@@ -63,6 +63,9 @@
     <t>Attention drifting from the task to unrelated content.</t>
   </si>
   <si>
+    <t>Children encouraging or reassuring each other (or themselves).</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -78,17 +81,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Emotion-drive reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Children encouraging or reassuring each other (or themselves).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF966450"/>
+      <t xml:space="preserve"> Overload-driven reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Expressing being overwhelmed by the amount of text, results, or task difficulty.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF463CC8"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -100,11 +103,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Overload-driven reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Expressing being overwhelmed by the amount of text, results, or task difficulty.</t>
+      <t xml:space="preserve"> Deference-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Collaborative/Social reasoning</t>
+  </si>
+  <si>
+    <t>One child’s assertion of certainty overrides the peer’s doubt.</t>
   </si>
   <si>
     <r>
@@ -122,14 +128,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Deference-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Collaborative/Social reasoning</t>
-  </si>
-  <si>
-    <t>One child’s assertion of certainty overrides the peer’s doubt.</t>
+      <t xml:space="preserve"> Disagreement-driven reasoning</t>
+    </r>
   </si>
   <si>
     <r>
@@ -147,8 +147,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Disagreement-driven reasoning</t>
-    </r>
+      <t xml:space="preserve"> Individual reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>One child thinks and acts alone, without involving the partner in the decision.</t>
   </si>
   <si>
     <r>
@@ -166,17 +169,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Individual reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>One child thinks and acts alone, without involving the partner in the decision.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF463CC8"/>
+      <t xml:space="preserve"> Negotiated reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Jointly deciding what to do by proposing and agreeing on the next step.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -188,11 +191,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Negotiated reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Jointly deciding what to do by proposing and agreeing on the next step.</t>
+      <t xml:space="preserve"> Disengagement Reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Metacognitive monitoring</t>
+  </si>
+  <si>
+    <t>Explicitly leaving or avoiding a resource.</t>
   </si>
   <si>
     <r>
@@ -210,14 +216,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Disengagement Reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Metacognitive monitoring</t>
-  </si>
-  <si>
-    <t>Explicitly leaving or avoiding a resource.</t>
+      <t xml:space="preserve"> Self-corrective reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Catching and fixing one’s own mistake.</t>
   </si>
   <si>
     <r>
@@ -235,11 +238,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Self-corrective reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Catching and fixing one’s own mistake.</t>
+      <t xml:space="preserve"> Strategy revision</t>
+    </r>
+  </si>
+  <si>
+    <t>Recognizing that a query returned nothing useful and deliberately changing the search approach (new wording, shorter query, different terms).</t>
   </si>
   <si>
     <r>
@@ -257,17 +260,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Strategy revision</t>
-    </r>
-  </si>
-  <si>
-    <t>Recognizing that a query returned nothing useful and deliberately changing the search approach (new wording, shorter query, different terms).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
+      <t xml:space="preserve"> Verification Reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Reasoning about the source or the drafted answer to check accuracy before submitting.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDC0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -279,17 +282,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Verification Reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Reasoning about the source or the drafted answer to check accuracy before submitting.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFDC0000"/>
+      <t xml:space="preserve"> Reward-driven reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Motivational reasoning</t>
+  </si>
+  <si>
+    <t>Reasoning about how answering affects the game reward.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -301,20 +307,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Reward-driven reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Motivational reasoning</t>
-  </si>
-  <si>
-    <t>Reasoning about how answering affects the game reward.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFDC0000"/>
+      <t xml:space="preserve"> Experience-basd reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Prior-knowledge reasoning</t>
+  </si>
+  <si>
+    <t>Drawing on first-hand or past experience to interpret the task or judge an answer.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -326,8 +332,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Task completition urgency</t>
-    </r>
+      <t xml:space="preserve"> Memory-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Retrieving an answer from earlier actions during the activity.</t>
   </si>
   <si>
     <r>
@@ -345,20 +354,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Experience-basd reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Prior-knowledge reasoning</t>
-  </si>
-  <si>
-    <t>Drawing on first-hand or past experience to interpret the task or judge an answer.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
+      <t xml:space="preserve"> Recall-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Retrieving an answer from memory or classroom knowledge before or instead of searching.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFBE00"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -370,17 +376,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Memory-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Retrieving an answer from earlier actions during the activity.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
+      <t xml:space="preserve"> Completeness-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantitative reasoning</t>
+  </si>
+  <si>
+    <t>Deciding whether the answer fully satisfied the question.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFBE00"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -392,17 +401,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Recall-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Retrieving an answer from memory or classroom knowledge before or instead of searching.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFBE00"/>
+      <t xml:space="preserve"> Count-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Monitoring progress against a required number of items to decide on stopping.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -414,20 +423,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Completeness-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Quantitative reasoning</t>
-  </si>
-  <si>
-    <t>Deciding whether the answer fully satisfied the question.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFBE00"/>
+      <t xml:space="preserve"> Error-driven reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Semantic reasoning</t>
+  </si>
+  <si>
+    <t>Misreading a word’s role or referent in the task or a snippet.</t>
+  </si>
+  <si>
+    <t>Deliberating which words to keep in the query or to add in the answer</t>
+  </si>
+  <si>
+    <t>Attention to spelling and the exact written form of words</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006EFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -439,17 +454,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Count-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Monitoring progress against a required number of items to decide on stopping.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
+      <t xml:space="preserve"> Comparative reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Using specific evidence to choose between competing answers.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006EFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -461,23 +476,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Error-driven reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Semantic reasoning</t>
-  </si>
-  <si>
-    <t>Misreading a word’s role or referent in the task or a snippet.</t>
-  </si>
-  <si>
-    <t>Deliberating which words to keep in the query or to add in the answer</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
+      <t xml:space="preserve"> Cross-source Reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Looking for another source before accepting the answer.</t>
+  </si>
+  <si>
+    <t>Reasoning about how trustworthy a source seems.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006EFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -489,11 +501,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Ortographic reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Attention to spelling and the exact written form of words</t>
+      <t xml:space="preserve"> Text-based reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Judging relevance, or extracting the information, by focusing on the text (snippet, title, or page body).</t>
   </si>
   <si>
     <r>
@@ -511,78 +523,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Comparative reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Source reasoning</t>
-  </si>
-  <si>
-    <t>Using specific evidence to choose between competing answers.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006EFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Cross-source Reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Looking for another source before accepting the answer.</t>
-  </si>
-  <si>
-    <t>Reasoning about how trustworthy a source seems.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006EFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Text-based reasoning</t>
-    </r>
-  </si>
-  <si>
-    <t>Judging relevance, or extracting the information, by focusing on the text (snippet, title, or page body).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006EFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> Visual-based reasoning</t>
     </r>
   </si>
@@ -665,12 +605,6 @@
     <t>Comparative reasoning</t>
   </si>
   <si>
-    <t>Orthographic reasoning</t>
-  </si>
-  <si>
-    <t>Formulation reasoning</t>
-  </si>
-  <si>
     <t>Error-driven reasoning</t>
   </si>
   <si>
@@ -833,19 +767,10 @@
     <t xml:space="preserve">   Orthographic-focused reasoning</t>
   </si>
   <si>
-    <t xml:space="preserve">   Query-term selection reasoning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Parsing error</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Completion-driven reasoning</t>
   </si>
   <si>
     <t xml:space="preserve">   Reward-driven reasoning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Memory-supported reasoning</t>
   </si>
   <si>
     <t xml:space="preserve">   Experience-based reasoning</t>
@@ -1385,39 +1310,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFDC0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Task completition urgency</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Gr=105</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -1678,62 +1570,6 @@
       </rPr>
       <t xml:space="preserve">
 Gr=27</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ortographic reasoning</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Gr=87</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>○Source Reasoning</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Gr=198</t>
     </r>
   </si>
   <si>
@@ -2465,18 +2301,188 @@
   </si>
   <si>
     <t>"Ma in questo sito il testo non dice niente!"</t>
+  </si>
+  <si>
+    <t>Source-based reasoning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ortographic-focused reasoning</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF966450"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Emotion-driven reasoning</t>
+    </r>
+  </si>
+  <si>
+    <t>Orthographic-based reasoning</t>
+  </si>
+  <si>
+    <t>Query-term reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Query-term reasoning</t>
+  </si>
+  <si>
+    <t>Error-based reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Memory-based reasoning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>○Source-based Reasoning</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Gr=198</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ortographic-focused reasoning</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Gr=87</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFDC0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completion-driven reasoning</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Gr=105</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDC0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Completion-driven reasoning</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3245,9 +3251,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3256,387 +3262,390 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="23" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="22" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="22" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="23" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="22" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="22" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="22" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="38" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3956,14 +3965,14 @@
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" style="127" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" style="109" customWidth="1"/>
     <col min="2" max="2" width="30.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" style="129" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="69.1640625" style="105" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="63.5" style="104" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" style="111" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="69.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63.5" style="87" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="75.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.5" style="1" bestFit="1" customWidth="1"/>
@@ -3971,1060 +3980,1060 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="121" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="130" t="s">
-        <v>68</v>
+      <c r="A1" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="112" t="s">
+        <v>64</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D1" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="130" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="131" t="s">
+      <c r="F1" s="113" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="112" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A2" s="104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="115"/>
+      <c r="C2" s="88">
+        <v>61</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="115">
+        <v>15</v>
+      </c>
+      <c r="F2" s="98"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="116"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="104"/>
+      <c r="B3" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="90">
+        <v>31</v>
+      </c>
+      <c r="D3" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="118">
+        <v>14</v>
+      </c>
+      <c r="F3" s="119" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="120" t="s">
+        <v>246</v>
+      </c>
+      <c r="H3" s="92" t="s">
+        <v>269</v>
+      </c>
+      <c r="I3" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="J3" s="120" t="s">
+        <v>240</v>
+      </c>
+      <c r="K3" s="127" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A4" s="104"/>
+      <c r="B4" s="91" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" s="90">
+        <v>28</v>
+      </c>
+      <c r="D4" s="91" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="118">
+        <v>12</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" s="122" t="s">
+        <v>247</v>
+      </c>
+      <c r="H4" s="92" t="s">
+        <v>270</v>
+      </c>
+      <c r="I4" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="J4" s="122" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="105"/>
+      <c r="B5" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="95">
+        <v>10</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="123">
+        <v>5</v>
+      </c>
+      <c r="F5" s="124" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="125" t="s">
+        <v>248</v>
+      </c>
+      <c r="H5" s="97" t="s">
+        <v>271</v>
+      </c>
+      <c r="I5" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="125" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="115"/>
+      <c r="C6" s="88">
+        <v>220</v>
+      </c>
+      <c r="D6" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="115">
+        <v>18</v>
+      </c>
+      <c r="F6" s="98"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="116"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="116"/>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A7" s="104"/>
+      <c r="B7" s="91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="90">
+        <v>51</v>
+      </c>
+      <c r="D7" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="118">
+        <v>16</v>
+      </c>
+      <c r="F7" s="119" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="120" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="127" t="s">
+        <v>272</v>
+      </c>
+      <c r="I7" s="128" t="s">
+        <v>208</v>
+      </c>
+      <c r="J7" s="120" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" s="127" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A8" s="104"/>
+      <c r="B8" s="91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="90">
+        <v>53</v>
+      </c>
+      <c r="D8" s="91" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="118">
+        <v>16</v>
+      </c>
+      <c r="F8" s="119" t="s">
+        <v>224</v>
+      </c>
+      <c r="G8" s="120" t="s">
+        <v>250</v>
+      </c>
+      <c r="H8" s="121" t="s">
+        <v>223</v>
+      </c>
+      <c r="I8" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="J8" s="120" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" s="136" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A9" s="104"/>
+      <c r="B9" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="90">
+        <v>17</v>
+      </c>
+      <c r="D9" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="118">
+        <v>11</v>
+      </c>
+      <c r="F9" s="119" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="H9" s="92" t="s">
+        <v>273</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="120" t="s">
+        <v>244</v>
+      </c>
+      <c r="K9" s="127" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="46" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="105"/>
+      <c r="B10" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="95">
+        <v>115</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="123">
+        <v>18</v>
+      </c>
+      <c r="F10" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="125" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="I10" s="123" t="s">
+        <v>208</v>
+      </c>
+      <c r="J10" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="K10" s="137" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="129"/>
+      <c r="C11" s="88">
+        <v>84</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="115">
+        <v>16</v>
+      </c>
+      <c r="F11" s="130"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="131"/>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A12" s="104"/>
+      <c r="B12" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="90">
+        <v>19</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="118">
+        <v>10</v>
+      </c>
+      <c r="F12" s="119" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12" s="122" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="121" t="s">
+        <v>195</v>
+      </c>
+      <c r="I12" s="118" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="101" t="s">
+        <v>292</v>
+      </c>
+      <c r="K12" s="136" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A13" s="104"/>
+      <c r="B13" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="90">
+        <v>18</v>
+      </c>
+      <c r="D13" s="91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="118">
+        <v>11</v>
+      </c>
+      <c r="F13" s="119" t="s">
+        <v>231</v>
+      </c>
+      <c r="G13" s="120" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" s="92" t="s">
+        <v>275</v>
+      </c>
+      <c r="I13" s="118" t="s">
+        <v>234</v>
+      </c>
+      <c r="J13" s="120" t="s">
+        <v>233</v>
+      </c>
+      <c r="K13" s="127" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A14" s="104"/>
+      <c r="B14" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="90">
+        <v>26</v>
+      </c>
+      <c r="D14" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="118">
+        <v>13</v>
+      </c>
+      <c r="F14" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="120" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" s="121" t="s">
+        <v>237</v>
+      </c>
+      <c r="I14" s="118" t="s">
+        <v>238</v>
+      </c>
+      <c r="J14" s="120" t="s">
+        <v>293</v>
+      </c>
+      <c r="K14" s="136" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="105"/>
+      <c r="B15" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="95">
+        <v>26</v>
+      </c>
+      <c r="D15" s="96" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="123">
+        <v>12</v>
+      </c>
+      <c r="F15" s="124" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="125" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="97" t="s">
+        <v>197</v>
+      </c>
+      <c r="I15" s="96" t="s">
+        <v>198</v>
+      </c>
+      <c r="J15" s="102" t="s">
+        <v>294</v>
+      </c>
+      <c r="K15" s="137" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="104" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="115"/>
+      <c r="C16" s="88">
+        <v>127</v>
+      </c>
+      <c r="D16" s="89" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="115">
+        <v>18</v>
+      </c>
+      <c r="F16" s="98"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="116"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A17" s="104"/>
+      <c r="B17" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="90">
+        <v>25</v>
+      </c>
+      <c r="D17" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="118">
+        <v>14</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>217</v>
+      </c>
+      <c r="G17" s="122" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="121" t="s">
+        <v>276</v>
+      </c>
+      <c r="I17" s="118" t="s">
+        <v>208</v>
+      </c>
+      <c r="J17" s="120" t="s">
+        <v>295</v>
+      </c>
+      <c r="K17" s="127" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="105"/>
+      <c r="B18" s="96" t="s">
+        <v>339</v>
+      </c>
+      <c r="C18" s="95">
+        <v>105</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="123">
+        <v>18</v>
+      </c>
+      <c r="F18" s="124" t="s">
+        <v>239</v>
+      </c>
+      <c r="G18" s="125" t="s">
+        <v>255</v>
+      </c>
+      <c r="H18" s="126" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="123" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="125" t="s">
+        <v>296</v>
+      </c>
+      <c r="K18" s="138" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="115"/>
+      <c r="C19" s="88">
+        <v>118</v>
+      </c>
+      <c r="D19" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="115">
+        <v>18</v>
+      </c>
+      <c r="F19" s="98"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="116"/>
+    </row>
+    <row r="20" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="104"/>
+      <c r="B20" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="90">
+        <v>56</v>
+      </c>
+      <c r="D20" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="118">
+        <v>15</v>
+      </c>
+      <c r="F20" s="119" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" s="122" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="121" t="s">
+        <v>278</v>
+      </c>
+      <c r="I20" s="118"/>
+      <c r="J20" s="122" t="s">
+        <v>301</v>
+      </c>
+      <c r="K20" s="127" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.15">
+      <c r="A21" s="104"/>
+      <c r="B21" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="90">
+        <v>77</v>
+      </c>
+      <c r="D21" s="91" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="118">
+        <v>17</v>
+      </c>
+      <c r="F21" s="119" t="s">
+        <v>218</v>
+      </c>
+      <c r="G21" s="120" t="s">
+        <v>257</v>
+      </c>
+      <c r="H21" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="I21" s="118" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" s="120" t="s">
+        <v>297</v>
+      </c>
+      <c r="K21" s="136" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="105"/>
+      <c r="B22" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="95">
+        <v>20</v>
+      </c>
+      <c r="D22" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="123">
+        <v>10</v>
+      </c>
+      <c r="F22" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="G22" s="125" t="s">
+        <v>258</v>
+      </c>
+      <c r="H22" s="126" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="123" t="s">
+        <v>207</v>
+      </c>
+      <c r="J22" s="125" t="s">
+        <v>298</v>
+      </c>
+      <c r="K22" s="137" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="104" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="115"/>
+      <c r="C23" s="88">
+        <v>57</v>
+      </c>
+      <c r="D23" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="115">
+        <v>18</v>
+      </c>
+      <c r="F23" s="98"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="116"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A24" s="104"/>
+      <c r="B24" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="90">
+        <v>28</v>
+      </c>
+      <c r="D24" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="118">
+        <v>15</v>
+      </c>
+      <c r="F24" s="119" t="s">
         <v>203</v>
       </c>
-      <c r="G1" s="130" t="s">
-        <v>118</v>
-      </c>
-      <c r="H1" s="132" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="130" t="s">
+      <c r="G24" s="120" t="s">
+        <v>259</v>
+      </c>
+      <c r="H24" s="92" t="s">
+        <v>281</v>
+      </c>
+      <c r="I24" s="118" t="s">
+        <v>205</v>
+      </c>
+      <c r="J24" s="122" t="s">
+        <v>300</v>
+      </c>
+      <c r="K24" s="136" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="106"/>
+      <c r="B25" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="95">
+        <v>33</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="123">
+        <v>16</v>
+      </c>
+      <c r="F25" s="124" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="125" t="s">
+        <v>260</v>
+      </c>
+      <c r="H25" s="97" t="s">
+        <v>282</v>
+      </c>
+      <c r="I25" s="123"/>
+      <c r="J25" s="125" t="s">
+        <v>299</v>
+      </c>
+      <c r="K25" s="138" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="115"/>
+      <c r="C26" s="88">
+        <v>179</v>
+      </c>
+      <c r="D26" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="115">
+        <v>18</v>
+      </c>
+      <c r="F26" s="98"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="116"/>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A27" s="104"/>
+      <c r="B27" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="90">
+        <v>27</v>
+      </c>
+      <c r="D27" s="91" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="118">
+        <v>13</v>
+      </c>
+      <c r="F27" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="122" t="s">
+        <v>261</v>
+      </c>
+      <c r="H27" s="121" t="s">
+        <v>283</v>
+      </c>
+      <c r="I27" s="118" t="s">
+        <v>222</v>
+      </c>
+      <c r="J27" s="122" t="s">
+        <v>302</v>
+      </c>
+      <c r="K27" s="127" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A28" s="104"/>
+      <c r="B28" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="90">
+        <v>74</v>
+      </c>
+      <c r="D28" s="91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="118">
+        <v>18</v>
+      </c>
+      <c r="F28" s="119" t="s">
+        <v>200</v>
+      </c>
+      <c r="G28" s="120" t="s">
+        <v>262</v>
+      </c>
+      <c r="H28" s="121" t="s">
+        <v>284</v>
+      </c>
+      <c r="I28" s="118" t="s">
+        <v>228</v>
+      </c>
+      <c r="J28" s="122" t="s">
+        <v>322</v>
+      </c>
+      <c r="K28" s="127" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="105"/>
+      <c r="B29" s="96" t="s">
+        <v>329</v>
+      </c>
+      <c r="C29" s="95">
+        <v>87</v>
+      </c>
+      <c r="D29" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="123">
+        <v>18</v>
+      </c>
+      <c r="F29" s="124" t="s">
+        <v>220</v>
+      </c>
+      <c r="G29" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="H29" s="126" t="s">
+        <v>285</v>
+      </c>
+      <c r="I29" s="123" t="s">
+        <v>211</v>
+      </c>
+      <c r="J29" s="125" t="s">
+        <v>303</v>
+      </c>
+      <c r="K29" s="137" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="104" t="s">
+        <v>328</v>
+      </c>
+      <c r="B30" s="115"/>
+      <c r="C30" s="88">
+        <v>198</v>
+      </c>
+      <c r="D30" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="115">
+        <v>18</v>
+      </c>
+      <c r="F30" s="98"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="116"/>
+    </row>
+    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+      <c r="A31" s="104"/>
+      <c r="B31" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="90">
+        <v>15</v>
+      </c>
+      <c r="D31" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="118">
+        <v>8</v>
+      </c>
+      <c r="F31" s="119" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="H31" s="121" t="s">
+        <v>201</v>
+      </c>
+      <c r="I31" s="118" t="s">
         <v>202</v>
       </c>
-      <c r="J1" s="130" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="132" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A2" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="106">
-        <v>61</v>
-      </c>
-      <c r="D2" s="107" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="133">
+      <c r="J31" s="120" t="s">
+        <v>304</v>
+      </c>
+      <c r="K31" s="136" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.15">
+      <c r="A32" s="104"/>
+      <c r="B32" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="90">
+        <v>49</v>
+      </c>
+      <c r="D32" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="118">
+        <v>14</v>
+      </c>
+      <c r="F32" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="120" t="s">
+        <v>265</v>
+      </c>
+      <c r="H32" s="92" t="s">
+        <v>286</v>
+      </c>
+      <c r="I32" s="118" t="s">
+        <v>211</v>
+      </c>
+      <c r="J32" s="120" t="s">
+        <v>305</v>
+      </c>
+      <c r="K32" s="136" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A33" s="107"/>
+      <c r="B33" s="91" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="90">
+        <v>70</v>
+      </c>
+      <c r="D33" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="118">
         <v>15</v>
       </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="134"/>
-    </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.15">
-      <c r="A3" s="122"/>
-      <c r="B3" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="108">
-        <v>31</v>
-      </c>
-      <c r="D3" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="136">
-        <v>14</v>
-      </c>
-      <c r="F3" s="137" t="s">
-        <v>224</v>
-      </c>
-      <c r="G3" s="138" t="s">
-        <v>258</v>
-      </c>
-      <c r="H3" s="110" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" s="109" t="s">
-        <v>225</v>
-      </c>
-      <c r="J3" s="138" t="s">
-        <v>252</v>
-      </c>
-      <c r="K3" s="145" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A4" s="122"/>
-      <c r="B4" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="108">
-        <v>28</v>
-      </c>
-      <c r="D4" s="109" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="136">
-        <v>12</v>
-      </c>
-      <c r="F4" s="137" t="s">
-        <v>226</v>
-      </c>
-      <c r="G4" s="140" t="s">
-        <v>259</v>
-      </c>
-      <c r="H4" s="110" t="s">
-        <v>282</v>
-      </c>
-      <c r="I4" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="J4" s="140" t="s">
-        <v>253</v>
-      </c>
-      <c r="K4" s="154" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="123"/>
-      <c r="B5" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="113">
-        <v>10</v>
-      </c>
-      <c r="D5" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="141">
-        <v>5</v>
-      </c>
-      <c r="F5" s="142" t="s">
-        <v>226</v>
-      </c>
-      <c r="G5" s="143" t="s">
-        <v>260</v>
-      </c>
-      <c r="H5" s="115" t="s">
-        <v>283</v>
-      </c>
-      <c r="I5" s="114" t="s">
-        <v>225</v>
-      </c>
-      <c r="J5" s="143" t="s">
-        <v>254</v>
-      </c>
-      <c r="K5" s="156" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="122" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="106">
-        <v>220</v>
-      </c>
-      <c r="D6" s="118" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="133">
+      <c r="F33" s="119" t="s">
+        <v>236</v>
+      </c>
+      <c r="G33" s="120" t="s">
+        <v>266</v>
+      </c>
+      <c r="H33" s="121" t="s">
+        <v>287</v>
+      </c>
+      <c r="I33" s="118" t="s">
+        <v>228</v>
+      </c>
+      <c r="J33" s="120" t="s">
+        <v>306</v>
+      </c>
+      <c r="K33" s="127" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A34" s="107"/>
+      <c r="B34" s="91" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="90">
+        <v>50</v>
+      </c>
+      <c r="D34" s="91" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="118">
         <v>18</v>
       </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="134"/>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A7" s="122"/>
-      <c r="B7" s="109" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="108">
+      <c r="F34" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="122" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" s="121" t="s">
+        <v>288</v>
+      </c>
+      <c r="I34" s="118" t="s">
+        <v>228</v>
+      </c>
+      <c r="J34" s="120" t="s">
+        <v>291</v>
+      </c>
+      <c r="K34" s="127" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="108"/>
+      <c r="B35" s="94" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="93">
+        <v>52</v>
+      </c>
+      <c r="D35" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="136">
+      <c r="E35" s="133">
         <v>16</v>
       </c>
-      <c r="F7" s="137" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="138" t="s">
-        <v>261</v>
-      </c>
-      <c r="H7" s="145" t="s">
-        <v>284</v>
-      </c>
-      <c r="I7" s="146" t="s">
-        <v>220</v>
-      </c>
-      <c r="J7" s="138" t="s">
-        <v>255</v>
-      </c>
-      <c r="K7" s="145" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A8" s="122"/>
-      <c r="B8" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="108">
-        <v>53</v>
-      </c>
-      <c r="D8" s="109" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="136">
-        <v>16</v>
-      </c>
-      <c r="F8" s="137" t="s">
-        <v>236</v>
-      </c>
-      <c r="G8" s="138" t="s">
-        <v>262</v>
-      </c>
-      <c r="H8" s="139" t="s">
-        <v>235</v>
-      </c>
-      <c r="I8" s="136" t="s">
-        <v>214</v>
-      </c>
-      <c r="J8" s="138" t="s">
-        <v>237</v>
-      </c>
-      <c r="K8" s="154" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A9" s="122"/>
-      <c r="B9" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="108">
-        <v>17</v>
-      </c>
-      <c r="D9" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="136">
-        <v>11</v>
-      </c>
-      <c r="F9" s="137" t="s">
+      <c r="F35" s="134" t="s">
+        <v>210</v>
+      </c>
+      <c r="G35" s="135" t="s">
+        <v>268</v>
+      </c>
+      <c r="H35" s="110" t="s">
+        <v>289</v>
+      </c>
+      <c r="I35" s="133" t="s">
         <v>205</v>
       </c>
-      <c r="G9" s="138" t="s">
-        <v>263</v>
-      </c>
-      <c r="H9" s="110" t="s">
-        <v>285</v>
-      </c>
-      <c r="I9" s="136" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" s="138" t="s">
-        <v>256</v>
-      </c>
-      <c r="K9" s="145" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="46" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="123"/>
-      <c r="B10" s="114" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="113">
-        <v>115</v>
-      </c>
-      <c r="D10" s="114" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="141">
-        <v>18</v>
-      </c>
-      <c r="F10" s="142" t="s">
-        <v>239</v>
-      </c>
-      <c r="G10" s="143" t="s">
-        <v>238</v>
-      </c>
-      <c r="H10" s="115" t="s">
-        <v>286</v>
-      </c>
-      <c r="I10" s="141" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" s="143" t="s">
-        <v>257</v>
-      </c>
-      <c r="K10" s="155" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="106">
-        <v>84</v>
-      </c>
-      <c r="D11" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="133">
-        <v>16</v>
-      </c>
-      <c r="F11" s="148"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="150"/>
-      <c r="K11" s="149"/>
-    </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A12" s="122"/>
-      <c r="B12" s="109" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="108">
-        <v>19</v>
-      </c>
-      <c r="D12" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="136">
-        <v>10</v>
-      </c>
-      <c r="F12" s="137" t="s">
-        <v>205</v>
-      </c>
-      <c r="G12" s="140" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="139" t="s">
-        <v>207</v>
-      </c>
-      <c r="I12" s="136" t="s">
-        <v>204</v>
-      </c>
-      <c r="J12" s="119" t="s">
-        <v>304</v>
-      </c>
-      <c r="K12" s="154" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A13" s="122"/>
-      <c r="B13" s="109" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="108">
-        <v>18</v>
-      </c>
-      <c r="D13" s="109" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="136">
-        <v>11</v>
-      </c>
-      <c r="F13" s="137" t="s">
-        <v>243</v>
-      </c>
-      <c r="G13" s="138" t="s">
-        <v>264</v>
-      </c>
-      <c r="H13" s="110" t="s">
-        <v>287</v>
-      </c>
-      <c r="I13" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="J13" s="138" t="s">
-        <v>245</v>
-      </c>
-      <c r="K13" s="145" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A14" s="122"/>
-      <c r="B14" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="108">
-        <v>26</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="136">
-        <v>13</v>
-      </c>
-      <c r="F14" s="137" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="138" t="s">
-        <v>265</v>
-      </c>
-      <c r="H14" s="139" t="s">
-        <v>249</v>
-      </c>
-      <c r="I14" s="136" t="s">
-        <v>250</v>
-      </c>
-      <c r="J14" s="138" t="s">
-        <v>305</v>
-      </c>
-      <c r="K14" s="154" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="123"/>
-      <c r="B15" s="114" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="113">
-        <v>26</v>
-      </c>
-      <c r="D15" s="114" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="141">
-        <v>12</v>
-      </c>
-      <c r="F15" s="142" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="143" t="s">
-        <v>208</v>
-      </c>
-      <c r="H15" s="115" t="s">
-        <v>209</v>
-      </c>
-      <c r="I15" s="114" t="s">
-        <v>210</v>
-      </c>
-      <c r="J15" s="120" t="s">
-        <v>306</v>
-      </c>
-      <c r="K15" s="155" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="122" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="106">
-        <v>127</v>
-      </c>
-      <c r="D16" s="107" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="133">
-        <v>18</v>
-      </c>
-      <c r="F16" s="116"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="134"/>
-    </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A17" s="122"/>
-      <c r="B17" s="109" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="108">
-        <v>25</v>
-      </c>
-      <c r="D17" s="109" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="136">
-        <v>14</v>
-      </c>
-      <c r="F17" s="137" t="s">
-        <v>229</v>
-      </c>
-      <c r="G17" s="140" t="s">
-        <v>266</v>
-      </c>
-      <c r="H17" s="139" t="s">
-        <v>288</v>
-      </c>
-      <c r="I17" s="136" t="s">
-        <v>220</v>
-      </c>
-      <c r="J17" s="138" t="s">
+      <c r="J35" s="135" t="s">
+        <v>290</v>
+      </c>
+      <c r="K35" s="139" t="s">
         <v>307</v>
-      </c>
-      <c r="K17" s="145" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="123"/>
-      <c r="B18" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="113">
-        <v>105</v>
-      </c>
-      <c r="D18" s="114" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="141">
-        <v>18</v>
-      </c>
-      <c r="F18" s="142" t="s">
-        <v>251</v>
-      </c>
-      <c r="G18" s="143" t="s">
-        <v>267</v>
-      </c>
-      <c r="H18" s="144" t="s">
-        <v>289</v>
-      </c>
-      <c r="I18" s="141" t="s">
-        <v>210</v>
-      </c>
-      <c r="J18" s="143" t="s">
-        <v>308</v>
-      </c>
-      <c r="K18" s="156" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="122" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="106">
-        <v>118</v>
-      </c>
-      <c r="D19" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="133">
-        <v>18</v>
-      </c>
-      <c r="F19" s="116"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="134"/>
-    </row>
-    <row r="20" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="122"/>
-      <c r="B20" s="109" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="108">
-        <v>56</v>
-      </c>
-      <c r="D20" s="109" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="136">
-        <v>15</v>
-      </c>
-      <c r="F20" s="137" t="s">
-        <v>212</v>
-      </c>
-      <c r="G20" s="140" t="s">
-        <v>268</v>
-      </c>
-      <c r="H20" s="139" t="s">
-        <v>290</v>
-      </c>
-      <c r="I20" s="136"/>
-      <c r="J20" s="140" t="s">
-        <v>313</v>
-      </c>
-      <c r="K20" s="145" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.15">
-      <c r="A21" s="122"/>
-      <c r="B21" s="109" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="108">
-        <v>77</v>
-      </c>
-      <c r="D21" s="109" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="136">
-        <v>17</v>
-      </c>
-      <c r="F21" s="137" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="138" t="s">
-        <v>269</v>
-      </c>
-      <c r="H21" s="139" t="s">
-        <v>291</v>
-      </c>
-      <c r="I21" s="136" t="s">
-        <v>231</v>
-      </c>
-      <c r="J21" s="138" t="s">
-        <v>309</v>
-      </c>
-      <c r="K21" s="154" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="123"/>
-      <c r="B22" s="114" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="113">
-        <v>20</v>
-      </c>
-      <c r="D22" s="114" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="141">
-        <v>10</v>
-      </c>
-      <c r="F22" s="142" t="s">
-        <v>241</v>
-      </c>
-      <c r="G22" s="143" t="s">
-        <v>270</v>
-      </c>
-      <c r="H22" s="144" t="s">
-        <v>292</v>
-      </c>
-      <c r="I22" s="141" t="s">
-        <v>219</v>
-      </c>
-      <c r="J22" s="143" t="s">
-        <v>310</v>
-      </c>
-      <c r="K22" s="155" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="122" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="106">
-        <v>57</v>
-      </c>
-      <c r="D23" s="107" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="133">
-        <v>18</v>
-      </c>
-      <c r="F23" s="116"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="134"/>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A24" s="122"/>
-      <c r="B24" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="108">
-        <v>28</v>
-      </c>
-      <c r="D24" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="136">
-        <v>15</v>
-      </c>
-      <c r="F24" s="137" t="s">
-        <v>215</v>
-      </c>
-      <c r="G24" s="138" t="s">
-        <v>271</v>
-      </c>
-      <c r="H24" s="110" t="s">
-        <v>293</v>
-      </c>
-      <c r="I24" s="136" t="s">
-        <v>217</v>
-      </c>
-      <c r="J24" s="140" t="s">
-        <v>312</v>
-      </c>
-      <c r="K24" s="154" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="124"/>
-      <c r="B25" s="114" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="113">
-        <v>33</v>
-      </c>
-      <c r="D25" s="114" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="141">
-        <v>16</v>
-      </c>
-      <c r="F25" s="142" t="s">
-        <v>229</v>
-      </c>
-      <c r="G25" s="143" t="s">
-        <v>272</v>
-      </c>
-      <c r="H25" s="115" t="s">
-        <v>294</v>
-      </c>
-      <c r="I25" s="141"/>
-      <c r="J25" s="143" t="s">
-        <v>311</v>
-      </c>
-      <c r="K25" s="156" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="133"/>
-      <c r="C26" s="106">
-        <v>179</v>
-      </c>
-      <c r="D26" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="133">
-        <v>18</v>
-      </c>
-      <c r="F26" s="116"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="135"/>
-      <c r="K26" s="134"/>
-    </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A27" s="122"/>
-      <c r="B27" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="108">
-        <v>27</v>
-      </c>
-      <c r="D27" s="109" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="136">
-        <v>13</v>
-      </c>
-      <c r="F27" s="137" t="s">
-        <v>222</v>
-      </c>
-      <c r="G27" s="140" t="s">
-        <v>273</v>
-      </c>
-      <c r="H27" s="139" t="s">
-        <v>295</v>
-      </c>
-      <c r="I27" s="136" t="s">
-        <v>234</v>
-      </c>
-      <c r="J27" s="140" t="s">
-        <v>314</v>
-      </c>
-      <c r="K27" s="145" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.15">
-      <c r="A28" s="122"/>
-      <c r="B28" s="109" t="s">
-        <v>197</v>
-      </c>
-      <c r="C28" s="108">
-        <v>74</v>
-      </c>
-      <c r="D28" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="136">
-        <v>18</v>
-      </c>
-      <c r="F28" s="137" t="s">
-        <v>212</v>
-      </c>
-      <c r="G28" s="138" t="s">
-        <v>274</v>
-      </c>
-      <c r="H28" s="139" t="s">
-        <v>296</v>
-      </c>
-      <c r="I28" s="136" t="s">
-        <v>240</v>
-      </c>
-      <c r="J28" s="140" t="s">
-        <v>334</v>
-      </c>
-      <c r="K28" s="145" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="123"/>
-      <c r="B29" s="114" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="113">
-        <v>87</v>
-      </c>
-      <c r="D29" s="114" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="141">
-        <v>18</v>
-      </c>
-      <c r="F29" s="142" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="143" t="s">
-        <v>275</v>
-      </c>
-      <c r="H29" s="144" t="s">
-        <v>297</v>
-      </c>
-      <c r="I29" s="141" t="s">
-        <v>223</v>
-      </c>
-      <c r="J29" s="143" t="s">
-        <v>315</v>
-      </c>
-      <c r="K29" s="155" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="31" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="122" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="133"/>
-      <c r="C30" s="106">
-        <v>198</v>
-      </c>
-      <c r="D30" s="107" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="133">
-        <v>18</v>
-      </c>
-      <c r="F30" s="116"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="133"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="134"/>
-    </row>
-    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.15">
-      <c r="A31" s="122"/>
-      <c r="B31" s="109" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="108">
-        <v>15</v>
-      </c>
-      <c r="D31" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="136">
-        <v>8</v>
-      </c>
-      <c r="F31" s="137" t="s">
-        <v>212</v>
-      </c>
-      <c r="G31" s="138" t="s">
-        <v>276</v>
-      </c>
-      <c r="H31" s="139" t="s">
-        <v>213</v>
-      </c>
-      <c r="I31" s="136" t="s">
-        <v>214</v>
-      </c>
-      <c r="J31" s="138" t="s">
-        <v>316</v>
-      </c>
-      <c r="K31" s="154" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.15">
-      <c r="A32" s="122"/>
-      <c r="B32" s="109" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="108">
-        <v>49</v>
-      </c>
-      <c r="D32" s="109" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="136">
-        <v>14</v>
-      </c>
-      <c r="F32" s="137" t="s">
-        <v>222</v>
-      </c>
-      <c r="G32" s="138" t="s">
-        <v>277</v>
-      </c>
-      <c r="H32" s="110" t="s">
-        <v>298</v>
-      </c>
-      <c r="I32" s="136" t="s">
-        <v>223</v>
-      </c>
-      <c r="J32" s="138" t="s">
-        <v>317</v>
-      </c>
-      <c r="K32" s="154" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.15">
-      <c r="A33" s="125"/>
-      <c r="B33" s="109" t="s">
-        <v>247</v>
-      </c>
-      <c r="C33" s="108">
-        <v>70</v>
-      </c>
-      <c r="D33" s="109" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="136">
-        <v>15</v>
-      </c>
-      <c r="F33" s="137" t="s">
-        <v>248</v>
-      </c>
-      <c r="G33" s="138" t="s">
-        <v>278</v>
-      </c>
-      <c r="H33" s="139" t="s">
-        <v>299</v>
-      </c>
-      <c r="I33" s="136" t="s">
-        <v>240</v>
-      </c>
-      <c r="J33" s="138" t="s">
-        <v>318</v>
-      </c>
-      <c r="K33" s="145" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.15">
-      <c r="A34" s="125"/>
-      <c r="B34" s="109" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="108">
-        <v>50</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="136">
-        <v>18</v>
-      </c>
-      <c r="F34" s="137" t="s">
-        <v>222</v>
-      </c>
-      <c r="G34" s="140" t="s">
-        <v>279</v>
-      </c>
-      <c r="H34" s="139" t="s">
-        <v>300</v>
-      </c>
-      <c r="I34" s="136" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" s="138" t="s">
-        <v>303</v>
-      </c>
-      <c r="K34" s="145" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="126"/>
-      <c r="B35" s="112" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="111">
-        <v>52</v>
-      </c>
-      <c r="D35" s="112" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="151">
-        <v>16</v>
-      </c>
-      <c r="F35" s="152" t="s">
-        <v>222</v>
-      </c>
-      <c r="G35" s="153" t="s">
-        <v>280</v>
-      </c>
-      <c r="H35" s="128" t="s">
-        <v>301</v>
-      </c>
-      <c r="I35" s="151" t="s">
-        <v>217</v>
-      </c>
-      <c r="J35" s="153" t="s">
-        <v>302</v>
-      </c>
-      <c r="K35" s="157" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -5043,172 +5052,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="144" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="143" t="s">
+        <v>328</v>
+      </c>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="143" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="143" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="142"/>
+      <c r="Y1" s="143" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="143" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" s="141"/>
+      <c r="AF1" s="141"/>
+      <c r="AG1" s="142"/>
+      <c r="AH1" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="141"/>
+      <c r="AJ1" s="142"/>
+    </row>
+    <row r="2" spans="1:36" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.15">
+      <c r="A2" s="145"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="F2" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="89" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="89" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="87" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="89" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE1" s="87"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="89" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI1" s="87"/>
-      <c r="AJ1" s="88"/>
-    </row>
-    <row r="2" spans="1:36" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.15">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="62" t="s">
+      <c r="G2" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="H2" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="J2" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="K2" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="L2" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="I2" s="63" t="s">
+      <c r="M2" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O2" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="P2" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="63" t="s">
+      <c r="Q2" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="S2" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="63" t="s">
+      <c r="T2" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="63" t="s">
+      <c r="V2" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" s="63" t="s">
+      <c r="W2" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="X2" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="63" t="s">
+      <c r="Z2" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="R2" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="S2" s="63" t="s">
+      <c r="AA2" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="U2" s="63" t="s">
+      <c r="AB2" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="AC2" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="63" t="s">
+      <c r="AE2" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y2" s="63" t="s">
+      <c r="AF2" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="63" t="s">
+      <c r="AG2" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="63" t="s">
+      <c r="AI2" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC2" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD2" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE2" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF2" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG2" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI2" s="63" t="s">
-        <v>96</v>
-      </c>
       <c r="AJ2" s="66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="64" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B3" s="4">
         <v>3</v>
@@ -5318,7 +5327,7 @@
     </row>
     <row r="4" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="64" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
@@ -5428,7 +5437,7 @@
     </row>
     <row r="5" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="64" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
@@ -5538,7 +5547,7 @@
     </row>
     <row r="6" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="64" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
@@ -5648,7 +5657,7 @@
     </row>
     <row r="7" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="64" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B7" s="4">
         <v>3</v>
@@ -5758,7 +5767,7 @@
     </row>
     <row r="8" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="64" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B8" s="4">
         <v>3</v>
@@ -5868,7 +5877,7 @@
     </row>
     <row r="9" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="64" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B9" s="4">
         <v>3</v>
@@ -5978,7 +5987,7 @@
     </row>
     <row r="10" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="64" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B10" s="4">
         <v>3</v>
@@ -6088,7 +6097,7 @@
     </row>
     <row r="11" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="64" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B11" s="4">
         <v>4</v>
@@ -6198,7 +6207,7 @@
     </row>
     <row r="12" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="64" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B12" s="4">
         <v>4</v>
@@ -6308,7 +6317,7 @@
     </row>
     <row r="13" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="64" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B13" s="4">
         <v>4</v>
@@ -6418,7 +6427,7 @@
     </row>
     <row r="14" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="64" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -6528,7 +6537,7 @@
     </row>
     <row r="15" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="64" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B15" s="4">
         <v>4</v>
@@ -6638,7 +6647,7 @@
     </row>
     <row r="16" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="64" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B16" s="4">
         <v>4</v>
@@ -6748,7 +6757,7 @@
     </row>
     <row r="17" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="64" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
@@ -6858,7 +6867,7 @@
     </row>
     <row r="18" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="64" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B18" s="4">
         <v>4</v>
@@ -6968,7 +6977,7 @@
     </row>
     <row r="19" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="64" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7078,7 +7087,7 @@
     </row>
     <row r="20" spans="1:36" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="64" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B20" s="4">
         <v>3</v>
@@ -7188,7 +7197,7 @@
     </row>
     <row r="21" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="69" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B21" s="73"/>
       <c r="C21" s="69">
@@ -7333,18 +7342,18 @@
       <c r="AJ22" s="4"/>
     </row>
     <row r="23" spans="1:36" ht="46" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="86" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="86"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="86"/>
-      <c r="J23" s="86"/>
+      <c r="A23" s="140" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -7408,56 +7417,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="148" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="151"/>
+      <c r="D1" s="152" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="151"/>
+      <c r="F1" s="152" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" s="150"/>
+      <c r="H1" s="153" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="154"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="149"/>
+      <c r="B2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="96" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98" t="s">
-        <v>123</v>
-      </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="98" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" s="96"/>
-      <c r="H1" s="99" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" s="100"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="95"/>
-      <c r="B2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="12">
         <f>SUM(B4:B7)</f>
@@ -7493,8 +7502,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="103" t="s">
-        <v>200</v>
+      <c r="A4" s="86" t="s">
+        <v>188</v>
       </c>
       <c r="B4" s="19">
         <v>44.190475463867188</v>
@@ -7527,7 +7536,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B5" s="19">
         <v>20.517007827758789</v>
@@ -7560,7 +7569,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B6" s="19">
         <v>22.095237731933594</v>
@@ -7593,7 +7602,7 @@
     </row>
     <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B7" s="24">
         <v>17.360544204711914</v>
@@ -7626,7 +7635,7 @@
     </row>
     <row r="8" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>47</v>
+        <v>328</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B9:B13)</f>
@@ -7663,7 +7672,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B9" s="19">
         <v>26.829931259155273</v>
@@ -7696,7 +7705,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B10" s="19">
         <v>7.8911561965942383</v>
@@ -7729,7 +7738,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B11" s="19">
         <v>33.142856597900391</v>
@@ -7762,7 +7771,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B12" s="19">
         <v>29.986394882202148</v>
@@ -7795,7 +7804,7 @@
     </row>
     <row r="13" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B13" s="24">
         <v>6.312924861907959</v>
@@ -7828,7 +7837,7 @@
     </row>
     <row r="14" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="30">
         <f>SUM(B15:B17)</f>
@@ -7865,7 +7874,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B15" s="19">
         <v>34.721088409423828</v>
@@ -7897,8 +7906,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
-        <v>137</v>
+      <c r="A16" s="158" t="s">
+        <v>333</v>
       </c>
       <c r="B16" s="19">
         <v>28.408163070678711</v>
@@ -7930,8 +7939,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>138</v>
+      <c r="A17" s="159" t="s">
+        <v>334</v>
       </c>
       <c r="B17" s="24">
         <v>9.4693880081176758</v>
@@ -7964,7 +7973,7 @@
     </row>
     <row r="18" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="30">
         <f>SUM(B19:B20)</f>
@@ -8001,7 +8010,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B19" s="19">
         <v>58.394557952880859</v>
@@ -8034,7 +8043,7 @@
     </row>
     <row r="20" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B20" s="24">
         <v>11.047618865966797</v>
@@ -8067,7 +8076,7 @@
     </row>
     <row r="21" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A21" s="29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" s="30">
         <f>SUM(B22:B24)</f>
@@ -8103,8 +8112,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>141</v>
+      <c r="A22" s="158" t="s">
+        <v>335</v>
       </c>
       <c r="B22" s="19">
         <v>23.673469543457031</v>
@@ -8137,7 +8146,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B23" s="19">
         <v>22.095237731933594</v>
@@ -8170,7 +8179,7 @@
     </row>
     <row r="24" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B24" s="24">
         <v>4.7346940040588379</v>
@@ -8203,7 +8212,7 @@
     </row>
     <row r="25" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B25" s="30">
         <f>SUM(B26:B29)</f>
@@ -8240,7 +8249,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B26" s="19">
         <v>7.8911561965942383</v>
@@ -8273,7 +8282,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B27" s="19">
         <v>3.1564629077911377</v>
@@ -8306,7 +8315,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B28" s="19">
         <v>4.7346940040588379</v>
@@ -8339,7 +8348,7 @@
     </row>
     <row r="29" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B29" s="24">
         <v>6.312924861907959</v>
@@ -8409,7 +8418,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B31" s="19">
         <v>3.1564629077911377</v>
@@ -8442,7 +8451,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B32" s="19">
         <v>6.312924861907959</v>
@@ -8475,7 +8484,7 @@
     </row>
     <row r="33" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B33" s="24">
         <v>3.1564629077911377</v>
@@ -8508,7 +8517,7 @@
     </row>
     <row r="34" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A34" s="29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="30">
         <f>SUM(B35:B36)</f>
@@ -8545,7 +8554,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="18" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B35" s="19">
         <v>11.047618865966797</v>
@@ -8578,7 +8587,7 @@
     </row>
     <row r="36" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B36" s="34">
         <v>17.360544204711914</v>
@@ -8634,7 +8643,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8670D3-9798-F947-84D7-88A8EAF63494}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
@@ -8649,33 +8658,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G1" s="45" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="H1" s="45" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="52" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="48">
@@ -8700,7 +8709,7 @@
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A3" s="53"/>
       <c r="B3" s="46" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C3" s="75">
         <v>3</v>
@@ -8724,7 +8733,7 @@
     <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A4" s="53"/>
       <c r="B4" s="46" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C4" s="75">
         <v>1</v>
@@ -8748,7 +8757,7 @@
     <row r="5" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="58"/>
       <c r="B5" s="59" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C5" s="76">
         <v>1</v>
@@ -8771,7 +8780,7 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A6" s="54" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="56">
@@ -8796,7 +8805,7 @@
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A7" s="54"/>
       <c r="B7" s="46" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C7" s="75">
         <v>2</v>
@@ -8820,7 +8829,7 @@
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A8" s="54"/>
       <c r="B8" s="46" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C8" s="75">
         <v>0</v>
@@ -8844,7 +8853,7 @@
     <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A9" s="54"/>
       <c r="B9" s="46" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C9" s="75">
         <v>2</v>
@@ -8868,7 +8877,7 @@
     <row r="10" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="61"/>
       <c r="B10" s="59" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C10" s="81">
         <v>4</v>
@@ -8891,7 +8900,7 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A11" s="54" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B11" s="55"/>
       <c r="C11" s="56">
@@ -8916,7 +8925,7 @@
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A12" s="54"/>
       <c r="B12" s="46" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C12" s="75">
         <v>0</v>
@@ -8940,7 +8949,7 @@
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A13" s="54"/>
       <c r="B13" s="46" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C13" s="75">
         <v>0</v>
@@ -8964,7 +8973,7 @@
     <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.15">
       <c r="A14" s="54"/>
       <c r="B14" s="46" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C14" s="80">
         <v>2</v>
@@ -8988,7 +8997,7 @@
     <row r="15" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="61"/>
       <c r="B15" s="59" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C15" s="76">
         <v>0</v>
@@ -9011,7 +9020,7 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A16" s="54" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B16" s="55"/>
       <c r="C16" s="56">
@@ -9033,10 +9042,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A17" s="54"/>
       <c r="B17" s="46" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C17" s="75">
         <v>0</v>
@@ -9057,10 +9066,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="61"/>
-      <c r="B18" s="59" t="s">
-        <v>173</v>
+      <c r="B18" s="160" t="s">
+        <v>338</v>
       </c>
       <c r="C18" s="81">
         <v>4</v>
@@ -9081,9 +9090,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A19" s="54" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="56">
@@ -9105,10 +9114,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A20" s="54"/>
       <c r="B20" s="46" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C20" s="80">
         <v>7</v>
@@ -9129,10 +9138,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A21" s="54"/>
       <c r="B21" s="46" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C21" s="80">
         <v>7</v>
@@ -9153,10 +9162,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="61"/>
       <c r="B22" s="59" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C22" s="76">
         <v>1</v>
@@ -9177,9 +9186,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A23" s="54" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B23" s="55"/>
       <c r="C23" s="56">
@@ -9201,10 +9210,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A24" s="54"/>
       <c r="B24" s="46" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C24" s="75">
         <v>0</v>
@@ -9225,10 +9234,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="61"/>
       <c r="B25" s="59" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C25" s="76">
         <v>0</v>
@@ -9249,9 +9258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A26" s="54" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B26" s="55"/>
       <c r="C26" s="56">
@@ -9272,11 +9281,12 @@
       <c r="H26" s="57">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+      <c r="J26" s="42"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A27" s="54"/>
       <c r="B27" s="46" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C27" s="75">
         <v>0</v>
@@ -9297,10 +9307,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.15">
       <c r="A28" s="54"/>
       <c r="B28" s="84" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C28" s="80">
         <v>27</v>
@@ -9320,11 +9330,12 @@
       <c r="H28" s="50">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="157"/>
+    </row>
+    <row r="29" spans="1:10" ht="46" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="61"/>
-      <c r="B29" s="59" t="s">
-        <v>183</v>
+      <c r="B29" s="160" t="s">
+        <v>337</v>
       </c>
       <c r="C29" s="76">
         <v>0</v>
@@ -9344,10 +9355,11 @@
       <c r="H29" s="60">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="101" t="s">
-        <v>184</v>
+      <c r="J29" s="157"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="155" t="s">
+        <v>336</v>
       </c>
       <c r="B30" s="55"/>
       <c r="C30" s="56">
@@ -9369,10 +9381,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.15">
-      <c r="A31" s="101"/>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.15">
+      <c r="A31" s="155"/>
       <c r="B31" s="46" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C31" s="75">
         <v>0</v>
@@ -9393,10 +9405,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.15">
-      <c r="A32" s="101"/>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.15">
+      <c r="A32" s="155"/>
       <c r="B32" s="46" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C32" s="75">
         <v>0</v>
@@ -9418,9 +9430,9 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.15">
-      <c r="A33" s="101"/>
+      <c r="A33" s="155"/>
       <c r="B33" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C33" s="75">
         <v>0</v>
@@ -9442,9 +9454,9 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.15">
-      <c r="A34" s="101"/>
+      <c r="A34" s="155"/>
       <c r="B34" s="46" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C34" s="75">
         <v>0</v>
@@ -9466,9 +9478,9 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="102"/>
+      <c r="A35" s="156"/>
       <c r="B35" s="51" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C35" s="77">
         <v>0</v>
@@ -9491,7 +9503,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C38" s="42">
         <f>SUM(C30,C26,C23,C19,C16,C11,C6,C2)</f>
